--- a/data/trans_orig/IP13_R2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si limitaron su actividad por síntomas en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>384</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>54051</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57125</t>
+          <t>57127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53959</t>
+          <t>53968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109874</t>
+          <t>109685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116830</t>
+          <t>116631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147182</t>
+          <t>147526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155398</t>
+          <t>155579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>163447</t>
+          <t>164567</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174959</t>
+          <t>175397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316289</t>
+          <t>315516</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329247</t>
+          <t>328715</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>28442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159100</t>
+          <t>158842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>168922</t>
+          <t>168598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>194913</t>
+          <t>195166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207059</t>
+          <t>207051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356996</t>
+          <t>357121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>373577</t>
+          <t>373798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17807</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29900</t>
+          <t>30578</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>257651</t>
+          <t>258650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269724</t>
+          <t>269809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286236</t>
+          <t>286968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299387</t>
+          <t>299451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>551040</t>
+          <t>550362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>566618</t>
+          <t>566309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51509</t>
+          <t>51166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77482</t>
+          <t>77859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>628873</t>
+          <t>630298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>646329</t>
+          <t>646466</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>713777</t>
+          <t>712732</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734977</t>
+          <t>733763</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1349106</t>
+          <t>1348729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1375079</t>
+          <t>1375422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_R2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R2_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6215</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1528</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3460</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47657</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44322</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49505</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55983</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54051</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57127</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58189</t>
+          <t>50766</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53968</t>
+          <t>48749</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60406</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>114172</t>
+          <t>98423</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109685</t>
+          <t>94624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116631</t>
+          <t>100730</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9176</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5795</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14928</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3720</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11773</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>147809</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>142057</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>151190</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>152282</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>147526</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>155579</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>170715</t>
+          <t>139271</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164567</t>
+          <t>134432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175397</t>
+          <t>142102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>322998</t>
+          <t>287080</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>315516</t>
+          <t>281058</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>328715</t>
+          <t>292163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,62 +1406,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10811</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6243</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17866</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8203</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4474</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14230</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17324</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>27093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1519,67 +1519,67 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>189315</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>182260</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>193883</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>164869</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>158842</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>168598</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>201766</t>
+          <t>166411</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>195166</t>
+          <t>160147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207051</t>
+          <t>170196</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>366636</t>
+          <t>355726</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>357121</t>
+          <t>347705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>373798</t>
+          <t>362327</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>21774</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>265348</t>
+          <t>281277</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258650</t>
+          <t>273993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269809</t>
+          <t>286454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>294024</t>
+          <t>246146</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286968</t>
+          <t>239717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299451</t>
+          <t>250244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>559371</t>
+          <t>527424</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>550362</t>
+          <t>518187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>566309</t>
+          <t>534113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34234</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26014</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44933</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>26858</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18874</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35042</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>35016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51166</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77859</t>
+          <t>74402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>666059</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>655360</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>674279</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>900</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>638482</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>630298</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>646466</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>724695</t>
+          <t>602594</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>712732</t>
+          <t>593817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>733763</t>
+          <t>609888</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1363177</t>
+          <t>1268652</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1348729</t>
+          <t>1254723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1375422</t>
+          <t>1279694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
